--- a/public_holiday/祝日入力シート（事務局用）.xlsx
+++ b/public_holiday/祝日入力シート（事務局用）.xlsx
@@ -1929,7 +1929,7 @@
     </row>
     <row r="205">
       <c r="A205" s="10">
-        <v>45658.0</v>
+        <v>46023.0</v>
       </c>
       <c r="B205" s="12" t="s">
         <v>31</v>
@@ -1937,7 +1937,7 @@
     </row>
     <row r="206">
       <c r="A206" s="10">
-        <v>45659.0</v>
+        <v>46024.0</v>
       </c>
       <c r="B206" s="12" t="s">
         <v>31</v>
@@ -1945,11 +1945,26 @@
     </row>
     <row r="207">
       <c r="A207" s="10">
-        <v>45660.0</v>
+        <v>46025.0</v>
       </c>
       <c r="B207" s="12" t="s">
         <v>31</v>
       </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="10"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="10"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="10"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="10"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="10"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/public_holiday/祝日入力シート（事務局用）.xlsx
+++ b/public_holiday/祝日入力シート（事務局用）.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="祝日" sheetId="1" r:id="rId3"/>
-    <sheet state="visible" name="休息時間計算" sheetId="2" r:id="rId4"/>
+    <sheet state="visible" name="祝日" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="休息時間計算" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="47">
   <si>
     <t>元日</t>
   </si>
@@ -261,6 +261,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
@@ -1952,19 +1956,305 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="10"/>
+      <c r="A208" s="10">
+        <v>46034.0</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="209">
-      <c r="A209" s="10"/>
+      <c r="A209" s="10">
+        <v>46064.0</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="210">
-      <c r="A210" s="10"/>
+      <c r="A210" s="10">
+        <v>46076.0</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="211">
-      <c r="A211" s="10"/>
+      <c r="A211" s="10">
+        <v>46101.0</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="212">
-      <c r="A212" s="10"/>
+      <c r="A212" s="10">
+        <v>46141.0</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="10">
+        <v>46145.0</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="10">
+        <v>46146.0</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="10">
+        <v>46147.0</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="10">
+        <v>46148.0</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="10">
+        <v>46223.0</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="10">
+        <v>46245.0</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="10">
+        <v>46286.0</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="10">
+        <v>46287.0</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="10">
+        <v>46288.0</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="10">
+        <v>46307.0</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="10">
+        <v>46329.0</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="10">
+        <v>46349.0</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="10">
+        <v>46385.0</v>
+      </c>
+      <c r="B225" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="10">
+        <v>46386.0</v>
+      </c>
+      <c r="B226" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="10">
+        <v>46387.0</v>
+      </c>
+      <c r="B227" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="10">
+        <v>46388.0</v>
+      </c>
+      <c r="B228" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="10">
+        <v>46389.0</v>
+      </c>
+      <c r="B229" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="10">
+        <v>46390.0</v>
+      </c>
+      <c r="B230" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="10">
+        <v>46398.0</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="10">
+        <v>46429.0</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="10">
+        <v>46441.0</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="10">
+        <v>46468.0</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="10">
+        <v>46506.0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="10">
+        <v>46510.0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="10">
+        <v>46511.0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="10">
+        <v>46512.0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="10">
+        <v>46587.0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="10">
+        <v>46610.0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="10">
+        <v>46650.0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="10">
+        <v>46653.0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="10">
+        <v>46671.0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="10">
+        <v>46694.0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="10">
+        <v>46714.0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="10">
+        <v>46750.0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="10">
+        <v>46751.0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="10">
+        <v>46752.0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="10">
+        <v>46753.0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="10">
+        <v>46754.0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="10">
+        <v>46755.0</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
